--- a/inputData/Experiments/inputDataEx5_3_10.xlsx
+++ b/inputData/Experiments/inputDataEx5_3_10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DA0F23-2D6B-421A-84A5-DC5A87FB507F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF842D8-998C-42AD-B42C-17E0A8FB7F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -820,7 +820,7 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -900,7 +900,7 @@
         <v>50</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>1</v>

--- a/inputData/Experiments/inputDataEx5_3_10.xlsx
+++ b/inputData/Experiments/inputDataEx5_3_10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF842D8-998C-42AD-B42C-17E0A8FB7F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4018C7-460D-417C-9E28-9F93ABA6616B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="2610" yWindow="1430" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -820,7 +820,7 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -900,7 +900,7 @@
         <v>50</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>1</v>

--- a/inputData/Experiments/inputDataEx5_3_10.xlsx
+++ b/inputData/Experiments/inputDataEx5_3_10.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DA0F23-2D6B-421A-84A5-DC5A87FB507F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3913895-AF21-DE45-BA76-E826D7879493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>type</t>
   </si>
@@ -514,7 +515,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -559,7 +560,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -680,7 +681,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1043,4 +1044,372 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADE5BBD-367C-4045-BD98-472B0A165E9C}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>72</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>93</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>41</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>88</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>79</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>55</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="13:24">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="13:24">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="13:24">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="13:24">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="13:24">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="13:24">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="13:24">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="13:24">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="13:24">
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="13:24">
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputData/Experiments/inputDataEx5_3_10.xlsx
+++ b/inputData/Experiments/inputDataEx5_3_10.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4018C7-460D-417C-9E28-9F93ABA6616B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD88BEF-FCB8-514F-905B-1AAED4C295C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1430" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="2620" yWindow="1440" windowWidth="14400" windowHeight="13380" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>type</t>
   </si>
@@ -514,7 +515,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -559,7 +560,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -680,7 +681,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1043,4 +1044,234 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905ECD97-C838-334B-9C6D-799FF3C46824}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>72</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>93</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>41</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>88</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>79</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>55</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>